--- a/arquivos/tecnologia_capacity.xlsx
+++ b/arquivos/tecnologia_capacity.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\NEW_NFV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\atualizacao nfv automatico\NEW_NFV\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF39F190-1294-4397-A0E0-D5F9CEDFC690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD885DB4-AEFD-41EB-B8DA-B85399C2604A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>ID</t>
   </si>
@@ -39,15 +39,9 @@
     <t>CAPACITY</t>
   </si>
   <si>
-    <t>DOCSIS 3.0</t>
-  </si>
-  <si>
     <t>DOCSIS 3.1</t>
   </si>
   <si>
-    <t>VIRTUA</t>
-  </si>
-  <si>
     <t>XGSPON RES RESID</t>
   </si>
   <si>
@@ -97,6 +91,15 @@
   </si>
   <si>
     <t>ESTACAO_ENTREGA</t>
+  </si>
+  <si>
+    <t>HFC BSOD</t>
+  </si>
+  <si>
+    <t>VIRTUA GPON</t>
+  </si>
+  <si>
+    <t>VIRTUA HFC</t>
   </si>
 </sst>
 </file>
@@ -414,10 +417,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
   </cols>
@@ -438,7 +441,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>50</v>
@@ -449,7 +452,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -460,7 +463,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -471,10 +474,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -482,10 +485,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -493,10 +496,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -504,10 +507,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -515,10 +518,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
         <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -526,10 +529,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -537,10 +540,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -548,10 +551,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -559,10 +562,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -570,10 +573,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -581,7 +584,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>500</v>
@@ -592,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>500</v>
@@ -603,10 +606,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
         <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -614,7 +617,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -625,10 +628,21 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
